--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R4a92e1adfea044d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R1b3a33fa3b004097"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R738c1c1789794eba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Racdbfe77549a4c21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Ra2408a2189e1428f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R0e2e671c6a0e4456"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R282fe71a91b84636"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R115a6aae4240432b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R139bf1079c2f4cf0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Ra4bbe0c0621e4799"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,10 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="@"/>
-    <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd&quot;T&quot;hh:mm:ss&quot;Z&quot;"/>
-    <x:numFmt numFmtId="202" formatCode="0"/>
+    <x:numFmt numFmtId="201" formatCode="0"/>
   </x:numFmts>
   <x:fonts count="3">
     <x:font>
@@ -90,7 +89,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -134,12 +133,6 @@
     <x:xf numFmtId="200" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="top" wrapText="1"/>
     </x:xf>
@@ -149,13 +142,13 @@
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="201" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="201" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="201" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -478,18 +471,18 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="54" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="56" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="50" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="66" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="62" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>对象或业务主键</x:v>
+        <x:v>交付物或数据库对象</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>字段</x:v>
+        <x:v>字段路径</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
         <x:v>正确值</x:v>
@@ -498,466 +491,74 @@
         <x:v>来源</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="32" customHeight="1">
+    <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="14" t="str">
-        <x:v>N001</x:v>
+        <x:v>output/notify_plan.db的send_plan</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>final_reason</x:v>
+        <x:v>action</x:v>
       </x:c>
       <x:c r="C2" s="16" t="str">
-        <x:v>NULL</x:v>
+        <x:v>send</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>candidate_decision</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="32" customHeight="1">
+        <x:v>裁决结果进入发送队列</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="38" customHeight="1">
       <x:c r="A3" s="13" t="str">
-        <x:v>N001</x:v>
+        <x:v>output/notify_plan.db的candidate_decision</x:v>
       </x:c>
       <x:c r="B3" s="13" t="str">
-        <x:v>local_time</x:v>
+        <x:v>event_id=N004的local_time|final_reason</x:v>
       </x:c>
       <x:c r="C3" s="17" t="str">
-        <x:v>16:00:00</x:v>
+        <x:v>03:06:00|quiet_hours</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
         <x:v>requested_at_utc与timezone_offset_min</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="32" customHeight="1">
+    <x:row r="4" ht="38" customHeight="1">
       <x:c r="A4" s="15" t="str">
-        <x:v>N002</x:v>
+        <x:v>output/notify_plan.db的repair_meta</x:v>
       </x:c>
       <x:c r="B4" s="15" t="str">
-        <x:v>final_reason</x:v>
+        <x:v>report_start_utc</x:v>
       </x:c>
       <x:c r="C4" s="18" t="str">
-        <x:v>duplicate_candidate</x:v>
+        <x:v>UTC时刻2026年7月30日00:00:00</x:v>
       </x:c>
       <x:c r="D4" s="15" t="str">
-        <x:v>candidate_decision</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="32" customHeight="1">
+        <x:v>rules/window_policy.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="38" customHeight="1">
       <x:c r="A5" s="13" t="str">
-        <x:v>N002</x:v>
+        <x:v>output/notify_plan.db的repair_meta</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>local_time</x:v>
+        <x:v>report_end_utc</x:v>
       </x:c>
       <x:c r="C5" s="17" t="str">
-        <x:v>16:03:00</x:v>
+        <x:v>UTC时刻2026年7月31日00:00:00</x:v>
       </x:c>
       <x:c r="D5" s="13" t="str">
-        <x:v>requested_at_utc与timezone_offset_min</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="32" customHeight="1">
+        <x:v>rules/window_policy.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="38" customHeight="1">
       <x:c r="A6" s="15" t="str">
-        <x:v>N003</x:v>
+        <x:v>output/notify_plan.db的repair_meta</x:v>
       </x:c>
       <x:c r="B6" s="15" t="str">
-        <x:v>final_reason</x:v>
+        <x:v>fixed_now_utc</x:v>
       </x:c>
       <x:c r="C6" s="18" t="str">
-        <x:v>NULL</x:v>
+        <x:v>UTC时刻2026年7月30日08:00:00</x:v>
       </x:c>
       <x:c r="D6" s="15" t="str">
-        <x:v>candidate_decision</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="32" customHeight="1">
-      <x:c r="A7" s="13" t="str">
-        <x:v>N003</x:v>
-      </x:c>
-      <x:c r="B7" s="13" t="str">
-        <x:v>local_time</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="str">
-        <x:v>16:04:00</x:v>
-      </x:c>
-      <x:c r="D7" s="13" t="str">
-        <x:v>requested_at_utc与timezone_offset_min</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="32" customHeight="1">
-      <x:c r="A8" s="15" t="str">
-        <x:v>N004</x:v>
-      </x:c>
-      <x:c r="B8" s="15" t="str">
-        <x:v>final_reason</x:v>
-      </x:c>
-      <x:c r="C8" s="18" t="str">
-        <x:v>quiet_hours</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="str">
-        <x:v>candidate_decision</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="32" customHeight="1">
-      <x:c r="A9" s="13" t="str">
-        <x:v>N004</x:v>
-      </x:c>
-      <x:c r="B9" s="13" t="str">
-        <x:v>local_time</x:v>
-      </x:c>
-      <x:c r="C9" s="17" t="str">
-        <x:v>03:06:00</x:v>
-      </x:c>
-      <x:c r="D9" s="13" t="str">
-        <x:v>requested_at_utc与timezone_offset_min</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="32" customHeight="1">
-      <x:c r="A10" s="15" t="str">
-        <x:v>N005</x:v>
-      </x:c>
-      <x:c r="B10" s="15" t="str">
-        <x:v>final_reason</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="str">
-        <x:v>subscriber_paused</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="str">
-        <x:v>candidate_decision</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="32" customHeight="1">
-      <x:c r="A11" s="13" t="str">
-        <x:v>N005</x:v>
-      </x:c>
-      <x:c r="B11" s="13" t="str">
-        <x:v>local_time</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="str">
-        <x:v>09:07:00</x:v>
-      </x:c>
-      <x:c r="D11" s="13" t="str">
-        <x:v>requested_at_utc与timezone_offset_min</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="32" customHeight="1">
-      <x:c r="A12" s="15" t="str">
-        <x:v>N006</x:v>
-      </x:c>
-      <x:c r="B12" s="15" t="str">
-        <x:v>final_reason</x:v>
-      </x:c>
-      <x:c r="C12" s="18" t="str">
-        <x:v>NULL</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="str">
-        <x:v>candidate_decision</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="32" customHeight="1">
-      <x:c r="A13" s="13" t="str">
-        <x:v>N006</x:v>
-      </x:c>
-      <x:c r="B13" s="13" t="str">
-        <x:v>local_time</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="str">
-        <x:v>08:08:00</x:v>
-      </x:c>
-      <x:c r="D13" s="13" t="str">
-        <x:v>requested_at_utc与timezone_offset_min</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="32" customHeight="1">
-      <x:c r="A14" s="15" t="str">
-        <x:v>N007</x:v>
-      </x:c>
-      <x:c r="B14" s="15" t="str">
-        <x:v>final_reason</x:v>
-      </x:c>
-      <x:c r="C14" s="18" t="str">
-        <x:v>tier_not_allowed</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="str">
-        <x:v>candidate_decision</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="32" customHeight="1">
-      <x:c r="A15" s="13" t="str">
-        <x:v>N007</x:v>
-      </x:c>
-      <x:c r="B15" s="13" t="str">
-        <x:v>local_time</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="str">
-        <x:v>16:09:00</x:v>
-      </x:c>
-      <x:c r="D15" s="13" t="str">
-        <x:v>requested_at_utc与timezone_offset_min</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="32" customHeight="1">
-      <x:c r="A16" s="15" t="str">
-        <x:v>N008</x:v>
-      </x:c>
-      <x:c r="B16" s="15" t="str">
-        <x:v>final_reason</x:v>
-      </x:c>
-      <x:c r="C16" s="18" t="str">
-        <x:v>manual_suppression</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="str">
-        <x:v>candidate_decision</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="32" customHeight="1">
-      <x:c r="A17" s="13" t="str">
-        <x:v>N008</x:v>
-      </x:c>
-      <x:c r="B17" s="13" t="str">
-        <x:v>local_time</x:v>
-      </x:c>
-      <x:c r="C17" s="17" t="str">
-        <x:v>16:10:00</x:v>
-      </x:c>
-      <x:c r="D17" s="13" t="str">
-        <x:v>requested_at_utc与timezone_offset_min</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="32" customHeight="1">
-      <x:c r="A18" s="15" t="str">
-        <x:v>N009</x:v>
-      </x:c>
-      <x:c r="B18" s="15" t="str">
-        <x:v>final_reason</x:v>
-      </x:c>
-      <x:c r="C18" s="18" t="str">
-        <x:v>user_daily_cap</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="str">
-        <x:v>candidate_decision</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="32" customHeight="1">
-      <x:c r="A19" s="13" t="str">
-        <x:v>N009</x:v>
-      </x:c>
-      <x:c r="B19" s="13" t="str">
-        <x:v>local_time</x:v>
-      </x:c>
-      <x:c r="C19" s="17" t="str">
-        <x:v>16:11:00</x:v>
-      </x:c>
-      <x:c r="D19" s="13" t="str">
-        <x:v>requested_at_utc与timezone_offset_min</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="32" customHeight="1">
-      <x:c r="A20" s="15" t="str">
-        <x:v>N010</x:v>
-      </x:c>
-      <x:c r="B20" s="15" t="str">
-        <x:v>final_reason</x:v>
-      </x:c>
-      <x:c r="C20" s="18" t="str">
-        <x:v>campaign_cap_reached</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="str">
-        <x:v>candidate_decision</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="32" customHeight="1">
-      <x:c r="A21" s="13" t="str">
-        <x:v>N010</x:v>
-      </x:c>
-      <x:c r="B21" s="13" t="str">
-        <x:v>local_time</x:v>
-      </x:c>
-      <x:c r="C21" s="17" t="str">
-        <x:v>08:12:00</x:v>
-      </x:c>
-      <x:c r="D21" s="13" t="str">
-        <x:v>requested_at_utc与timezone_offset_min</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="32" customHeight="1">
-      <x:c r="A22" s="15" t="str">
-        <x:v>N011</x:v>
-      </x:c>
-      <x:c r="B22" s="15" t="str">
-        <x:v>final_reason</x:v>
-      </x:c>
-      <x:c r="C22" s="18" t="str">
-        <x:v>NULL</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="str">
-        <x:v>candidate_decision</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="32" customHeight="1">
-      <x:c r="A23" s="13" t="str">
-        <x:v>N011</x:v>
-      </x:c>
-      <x:c r="B23" s="13" t="str">
-        <x:v>local_time</x:v>
-      </x:c>
-      <x:c r="C23" s="17" t="str">
-        <x:v>08:13:00</x:v>
-      </x:c>
-      <x:c r="D23" s="13" t="str">
-        <x:v>requested_at_utc与timezone_offset_min</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="32" customHeight="1">
-      <x:c r="A24" s="15" t="str">
-        <x:v>N012</x:v>
-      </x:c>
-      <x:c r="B24" s="15" t="str">
-        <x:v>final_reason</x:v>
-      </x:c>
-      <x:c r="C24" s="18" t="str">
-        <x:v>unknown_user</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="str">
-        <x:v>candidate_decision</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="32" customHeight="1">
-      <x:c r="A25" s="13" t="str">
-        <x:v>N012</x:v>
-      </x:c>
-      <x:c r="B25" s="13" t="str">
-        <x:v>local_time</x:v>
-      </x:c>
-      <x:c r="C25" s="17" t="str">
-        <x:v>08:14:00</x:v>
-      </x:c>
-      <x:c r="D25" s="13" t="str">
-        <x:v>requested_at_utc与timezone_offset_min</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="32" customHeight="1">
-      <x:c r="A26" s="15" t="str">
-        <x:v>N013</x:v>
-      </x:c>
-      <x:c r="B26" s="15" t="str">
-        <x:v>final_reason</x:v>
-      </x:c>
-      <x:c r="C26" s="18" t="str">
-        <x:v>unknown_campaign</x:v>
-      </x:c>
-      <x:c r="D26" s="15" t="str">
-        <x:v>candidate_decision</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="32" customHeight="1">
-      <x:c r="A27" s="13" t="str">
-        <x:v>N013</x:v>
-      </x:c>
-      <x:c r="B27" s="13" t="str">
-        <x:v>local_time</x:v>
-      </x:c>
-      <x:c r="C27" s="17" t="str">
-        <x:v>16:15:00</x:v>
-      </x:c>
-      <x:c r="D27" s="13" t="str">
-        <x:v>requested_at_utc与timezone_offset_min</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="32" customHeight="1">
-      <x:c r="A28" s="15" t="str">
-        <x:v>N014</x:v>
-      </x:c>
-      <x:c r="B28" s="15" t="str">
-        <x:v>final_reason</x:v>
-      </x:c>
-      <x:c r="C28" s="18" t="str">
-        <x:v>user_daily_cap</x:v>
-      </x:c>
-      <x:c r="D28" s="15" t="str">
-        <x:v>candidate_decision</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="32" customHeight="1">
-      <x:c r="A29" s="13" t="str">
-        <x:v>N014</x:v>
-      </x:c>
-      <x:c r="B29" s="13" t="str">
-        <x:v>local_time</x:v>
-      </x:c>
-      <x:c r="C29" s="17" t="str">
-        <x:v>08:16:00</x:v>
-      </x:c>
-      <x:c r="D29" s="13" t="str">
-        <x:v>requested_at_utc与timezone_offset_min</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="32" customHeight="1">
-      <x:c r="A30" s="15" t="str">
-        <x:v>N015</x:v>
-      </x:c>
-      <x:c r="B30" s="15" t="str">
-        <x:v>final_reason</x:v>
-      </x:c>
-      <x:c r="C30" s="18" t="str">
-        <x:v>already_delivered</x:v>
-      </x:c>
-      <x:c r="D30" s="15" t="str">
-        <x:v>candidate_decision</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="32" customHeight="1">
-      <x:c r="A31" s="13" t="str">
-        <x:v>N015</x:v>
-      </x:c>
-      <x:c r="B31" s="13" t="str">
-        <x:v>local_time</x:v>
-      </x:c>
-      <x:c r="C31" s="17" t="str">
-        <x:v>16:17:00</x:v>
-      </x:c>
-      <x:c r="D31" s="13" t="str">
-        <x:v>requested_at_utc与timezone_offset_min</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="32" customHeight="1">
-      <x:c r="A32" s="15" t="str">
-        <x:v>repair_meta</x:v>
-      </x:c>
-      <x:c r="B32" s="15" t="str">
-        <x:v>report_start_utc</x:v>
-      </x:c>
-      <x:c r="C32" s="19" t="n">
-        <x:v>46233</x:v>
-      </x:c>
-      <x:c r="D32" s="15" t="str">
-        <x:v>window_policy.json</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="32" customHeight="1">
-      <x:c r="A33" s="13" t="str">
-        <x:v>repair_meta</x:v>
-      </x:c>
-      <x:c r="B33" s="13" t="str">
-        <x:v>report_end_utc</x:v>
-      </x:c>
-      <x:c r="C33" s="20" t="n">
-        <x:v>46234</x:v>
-      </x:c>
-      <x:c r="D33" s="13" t="str">
-        <x:v>window_policy.json</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="32" customHeight="1">
-      <x:c r="A34" s="15" t="str">
-        <x:v>repair_meta</x:v>
-      </x:c>
-      <x:c r="B34" s="15" t="str">
-        <x:v>fixed_now_utc</x:v>
-      </x:c>
-      <x:c r="C34" s="19" t="n">
-        <x:v>46233.333333333336</x:v>
-      </x:c>
-      <x:c r="D34" s="15" t="str">
-        <x:v>window_policy.json</x:v>
+        <x:v>rules/window_policy.json</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1005,99 +606,225 @@
     </x:row>
     <x:row r="3" ht="50" customHeight="1">
       <x:c r="A3" s="13" t="str">
-        <x:v>抑制事件集合</x:v>
+        <x:v>duplicate_candidate事件</x:v>
       </x:c>
       <x:c r="B3" s="13" t="str">
         <x:v>event_id</x:v>
       </x:c>
       <x:c r="C3" s="13" t="str">
-        <x:v>N002；N004；N005；N007；N008；N009；N010；N012；N013；N014；N015</x:v>
+        <x:v>N002</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
-        <x:v>suppression_audit按时间排序</x:v>
+        <x:v>candidate_decision</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="50" customHeight="1">
       <x:c r="A4" s="15" t="str">
-        <x:v>发送计划列</x:v>
+        <x:v>quiet_hours事件</x:v>
       </x:c>
       <x:c r="B4" s="15" t="str">
-        <x:v>列名</x:v>
+        <x:v>event_id</x:v>
       </x:c>
       <x:c r="C4" s="15" t="str">
-        <x:v>event_id；user_id；campaign_id；channel；requested_at_utc；local_time；provider_message_id；send_priority；action</x:v>
+        <x:v>N004</x:v>
       </x:c>
       <x:c r="D4" s="15" t="str">
-        <x:v>report_schema.json</x:v>
+        <x:v>candidate_decision</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="50" customHeight="1">
       <x:c r="A5" s="13" t="str">
-        <x:v>抑制审计列</x:v>
+        <x:v>subscriber_paused事件</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>列名</x:v>
+        <x:v>event_id</x:v>
       </x:c>
       <x:c r="C5" s="13" t="str">
-        <x:v>event_id；user_id；campaign_id；channel；requested_at_utc；local_time；reason；detail</x:v>
+        <x:v>N005</x:v>
       </x:c>
       <x:c r="D5" s="13" t="str">
-        <x:v>report_schema.json</x:v>
+        <x:v>candidate_decision</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="50" customHeight="1">
       <x:c r="A6" s="15" t="str">
-        <x:v>配额报告列</x:v>
+        <x:v>tier_not_allowed事件</x:v>
       </x:c>
       <x:c r="B6" s="15" t="str">
-        <x:v>列名</x:v>
+        <x:v>event_id</x:v>
       </x:c>
       <x:c r="C6" s="15" t="str">
-        <x:v>campaign_id；channel；daily_cap；campaign_cap；existing_sent_count；planned_send_count；suppressed_count；remaining_after_plan</x:v>
+        <x:v>N007</x:v>
       </x:c>
       <x:c r="D6" s="15" t="str">
-        <x:v>report_schema.json</x:v>
+        <x:v>candidate_decision</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="50" customHeight="1">
       <x:c r="A7" s="13" t="str">
-        <x:v>派生表集合</x:v>
+        <x:v>manual_suppression事件</x:v>
       </x:c>
       <x:c r="B7" s="13" t="str">
-        <x:v>表名</x:v>
+        <x:v>event_id</x:v>
       </x:c>
       <x:c r="C7" s="13" t="str">
-        <x:v>candidate_decision；send_plan；suppression_audit；campaign_quota_report；repair_meta</x:v>
+        <x:v>N008</x:v>
       </x:c>
       <x:c r="D7" s="13" t="str">
-        <x:v>任务Prompt</x:v>
+        <x:v>candidate_decision</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="50" customHeight="1">
       <x:c r="A8" s="15" t="str">
-        <x:v>源表集合</x:v>
+        <x:v>user_daily_cap事件</x:v>
       </x:c>
       <x:c r="B8" s="15" t="str">
-        <x:v>表名</x:v>
+        <x:v>event_id</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>subscribers；campaign_rules；candidate_queue；delivery_history；suppression_overrides</x:v>
+        <x:v>N009；N014</x:v>
       </x:c>
       <x:c r="D8" s="15" t="str">
-        <x:v>notify_control.db</x:v>
+        <x:v>candidate_decision</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="50" customHeight="1">
       <x:c r="A9" s="13" t="str">
+        <x:v>campaign_cap_reached事件</x:v>
+      </x:c>
+      <x:c r="B9" s="13" t="str">
+        <x:v>event_id</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="str">
+        <x:v>N010</x:v>
+      </x:c>
+      <x:c r="D9" s="13" t="str">
+        <x:v>candidate_decision</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="50" customHeight="1">
+      <x:c r="A10" s="15" t="str">
+        <x:v>unknown_user事件</x:v>
+      </x:c>
+      <x:c r="B10" s="15" t="str">
+        <x:v>event_id</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="str">
+        <x:v>N012</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="str">
+        <x:v>candidate_decision</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="50" customHeight="1">
+      <x:c r="A11" s="13" t="str">
+        <x:v>unknown_campaign事件</x:v>
+      </x:c>
+      <x:c r="B11" s="13" t="str">
+        <x:v>event_id</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="str">
+        <x:v>N013</x:v>
+      </x:c>
+      <x:c r="D11" s="13" t="str">
+        <x:v>candidate_decision</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="50" customHeight="1">
+      <x:c r="A12" s="15" t="str">
+        <x:v>already_delivered事件</x:v>
+      </x:c>
+      <x:c r="B12" s="15" t="str">
+        <x:v>event_id</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="str">
+        <x:v>N015</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="str">
+        <x:v>candidate_decision</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="50" customHeight="1">
+      <x:c r="A13" s="13" t="str">
+        <x:v>发送计划列</x:v>
+      </x:c>
+      <x:c r="B13" s="13" t="str">
+        <x:v>列名</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="str">
+        <x:v>event_id；user_id；campaign_id；channel；requested_at_utc；local_time；provider_message_id；send_priority；action</x:v>
+      </x:c>
+      <x:c r="D13" s="13" t="str">
+        <x:v>report_schema.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="50" customHeight="1">
+      <x:c r="A14" s="15" t="str">
+        <x:v>抑制审计列</x:v>
+      </x:c>
+      <x:c r="B14" s="15" t="str">
+        <x:v>列名</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="str">
+        <x:v>event_id；user_id；campaign_id；channel；requested_at_utc；local_time；reason；detail</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="str">
+        <x:v>report_schema.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="50" customHeight="1">
+      <x:c r="A15" s="13" t="str">
+        <x:v>配额报告列</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="str">
+        <x:v>列名</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="str">
+        <x:v>campaign_id；channel；daily_cap；campaign_cap；existing_sent_count；planned_send_count；suppressed_count；remaining_after_plan</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="str">
+        <x:v>report_schema.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="50" customHeight="1">
+      <x:c r="A16" s="15" t="str">
+        <x:v>派生表集合</x:v>
+      </x:c>
+      <x:c r="B16" s="15" t="str">
+        <x:v>表名</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="str">
+        <x:v>candidate_decision；send_plan；suppression_audit；campaign_quota_report；repair_meta</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="str">
+        <x:v>Prompt声明的数据库交付</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="50" customHeight="1">
+      <x:c r="A17" s="13" t="str">
+        <x:v>源表集合</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="str">
+        <x:v>表名</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="str">
+        <x:v>subscribers；campaign_rules；candidate_queue；delivery_history；suppression_overrides</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="str">
+        <x:v>notify_control.db</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="50" customHeight="1">
+      <x:c r="A18" s="15" t="str">
         <x:v>原因集合</x:v>
       </x:c>
-      <x:c r="B9" s="13" t="str">
+      <x:c r="B18" s="15" t="str">
         <x:v>reason</x:v>
       </x:c>
-      <x:c r="C9" s="13" t="str">
+      <x:c r="C18" s="15" t="str">
         <x:v>unknown_user；unknown_campaign；already_delivered；subscriber_paused；manual_suppression；tier_not_allowed；quiet_hours；duplicate_candidate；user_daily_cap；campaign_cap_reached</x:v>
       </x:c>
-      <x:c r="D9" s="13" t="str">
+      <x:c r="D18" s="15" t="str">
         <x:v>decision_policy.csv</x:v>
       </x:c>
     </x:row>
@@ -1141,7 +868,7 @@
       <x:c r="B2" s="14" t="str">
         <x:v>候选总数</x:v>
       </x:c>
-      <x:c r="C2" s="24" t="n">
+      <x:c r="C2" s="22" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
@@ -1158,7 +885,7 @@
       <x:c r="B3" s="13" t="str">
         <x:v>发送总数</x:v>
       </x:c>
-      <x:c r="C3" s="25" t="n">
+      <x:c r="C3" s="23" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
@@ -1175,7 +902,7 @@
       <x:c r="B4" s="15" t="str">
         <x:v>抑制总数</x:v>
       </x:c>
-      <x:c r="C4" s="26" t="n">
+      <x:c r="C4" s="24" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D4" s="15" t="str">
@@ -1192,7 +919,7 @@
       <x:c r="B5" s="13" t="str">
         <x:v>活动数</x:v>
       </x:c>
-      <x:c r="C5" s="25" t="n">
+      <x:c r="C5" s="23" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D5" s="13" t="str">
@@ -1209,7 +936,7 @@
       <x:c r="B6" s="15" t="str">
         <x:v>existing_sent_count</x:v>
       </x:c>
-      <x:c r="C6" s="26" t="n">
+      <x:c r="C6" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="15" t="str">
@@ -1226,7 +953,7 @@
       <x:c r="B7" s="13" t="str">
         <x:v>planned_send_count</x:v>
       </x:c>
-      <x:c r="C7" s="25" t="n">
+      <x:c r="C7" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D7" s="13" t="str">
@@ -1243,7 +970,7 @@
       <x:c r="B8" s="15" t="str">
         <x:v>suppressed_count</x:v>
       </x:c>
-      <x:c r="C8" s="26" t="n">
+      <x:c r="C8" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D8" s="15" t="str">
@@ -1260,7 +987,7 @@
       <x:c r="B9" s="13" t="str">
         <x:v>remaining_after_plan</x:v>
       </x:c>
-      <x:c r="C9" s="25" t="n">
+      <x:c r="C9" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D9" s="13" t="str">
@@ -1277,7 +1004,7 @@
       <x:c r="B10" s="15" t="str">
         <x:v>existing_sent_count</x:v>
       </x:c>
-      <x:c r="C10" s="26" t="n">
+      <x:c r="C10" s="24" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D10" s="15" t="str">
@@ -1294,7 +1021,7 @@
       <x:c r="B11" s="13" t="str">
         <x:v>planned_send_count</x:v>
       </x:c>
-      <x:c r="C11" s="25" t="n">
+      <x:c r="C11" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D11" s="13" t="str">
@@ -1311,7 +1038,7 @@
       <x:c r="B12" s="15" t="str">
         <x:v>suppressed_count</x:v>
       </x:c>
-      <x:c r="C12" s="26" t="n">
+      <x:c r="C12" s="24" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D12" s="15" t="str">
@@ -1328,7 +1055,7 @@
       <x:c r="B13" s="13" t="str">
         <x:v>remaining_after_plan</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="n">
+      <x:c r="C13" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="13" t="str">
@@ -1345,7 +1072,7 @@
       <x:c r="B14" s="15" t="str">
         <x:v>existing_sent_count</x:v>
       </x:c>
-      <x:c r="C14" s="26" t="n">
+      <x:c r="C14" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="15" t="str">
@@ -1362,7 +1089,7 @@
       <x:c r="B15" s="13" t="str">
         <x:v>planned_send_count</x:v>
       </x:c>
-      <x:c r="C15" s="25" t="n">
+      <x:c r="C15" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D15" s="13" t="str">
@@ -1379,7 +1106,7 @@
       <x:c r="B16" s="15" t="str">
         <x:v>suppressed_count</x:v>
       </x:c>
-      <x:c r="C16" s="26" t="n">
+      <x:c r="C16" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="15" t="str">
@@ -1396,7 +1123,7 @@
       <x:c r="B17" s="13" t="str">
         <x:v>remaining_after_plan</x:v>
       </x:c>
-      <x:c r="C17" s="25" t="n">
+      <x:c r="C17" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="13" t="str">
@@ -1413,7 +1140,7 @@
       <x:c r="B18" s="15" t="str">
         <x:v>user_daily_cap</x:v>
       </x:c>
-      <x:c r="C18" s="26" t="n">
+      <x:c r="C18" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D18" s="15" t="str">
@@ -1430,7 +1157,7 @@
       <x:c r="B19" s="13" t="str">
         <x:v>其余九类原因</x:v>
       </x:c>
-      <x:c r="C19" s="25" t="n">
+      <x:c r="C19" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D19" s="13" t="str">
@@ -1473,7 +1200,7 @@
         <x:v>公用表表达式、临时视图、窗口函数和关联顺序可以不同</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>不能绕开SQLite实际计算或把event_id与最终原因逐项写死</x:v>
+        <x:v>裁决结果、预算累计与业务主键保持一致</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
@@ -1484,7 +1211,7 @@
         <x:v>可以增加不改变业务值的辅助索引</x:v>
       </x:c>
       <x:c r="C3" s="13" t="str">
-        <x:v>不能删除event_id和provider_message_id的唯一约束效果</x:v>
+        <x:v>event_id和provider_message_id仍具备唯一约束效果</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -1495,29 +1222,29 @@
         <x:v>允许UTF-8的LF或CRLF，必要字段可按CSV规范转义</x:v>
       </x:c>
       <x:c r="C4" s="15" t="str">
-        <x:v>列名、列序、业务行或规定排序不能变化</x:v>
+        <x:v>列名、列序、业务行和规定排序保持一致</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
       <x:c r="A5" s="13" t="str">
-        <x:v>数据库页布局</x:v>
+        <x:v>数据库物理布局</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>页号、空闲页、索引物理布局和文件哈希可以不同</x:v>
+        <x:v>页号、空闲页和索引分配可以不同</x:v>
       </x:c>
       <x:c r="C5" s="13" t="str">
-        <x:v>表结构、源表内容和派生业务行不能变化</x:v>
+        <x:v>表结构、源表内容和派生业务行保持一致</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
       <x:c r="A6" s="15" t="str">
-        <x:v>detail实现</x:v>
+        <x:v>detail生成方式</x:v>
       </x:c>
       <x:c r="B6" s="15" t="str">
         <x:v>可以在查询时关联decision_policy.csv导入的规则表</x:v>
       </x:c>
       <x:c r="C6" s="15" t="str">
-        <x:v>detail不能脱离规则文件或改写原因含义</x:v>
+        <x:v>detail与规则文件中的原因说明一致</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
@@ -1525,10 +1252,10 @@
         <x:v>运行日志</x:v>
       </x:c>
       <x:c r="B7" s="13" t="str">
-        <x:v>可输出SQLite版本、处理数量和错误定位信息</x:v>
+        <x:v>可记录SQLite版本、处理数量和错误定位信息</x:v>
       </x:c>
       <x:c r="C7" s="13" t="str">
-        <x:v>日志不能代替规定数据库、SQL或报表</x:v>
+        <x:v>规定数据库、SQL和报表仍需完整交付</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
@@ -1539,7 +1266,7 @@
         <x:v>可以使用临时表或临时视图</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>不能在交付数据库中残留含预制答案的无关表</x:v>
+        <x:v>交付数据库只保留与通知裁决有关的业务对象</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
